--- a/doc/测试用例设计文档.xlsx
+++ b/doc/测试用例设计文档.xlsx
@@ -226,10 +226,134 @@
     <t>系统已启动，处于登录页</t>
   </si>
   <si>
-    <t xml:space="preserve"> 1. 用户名输入框输入Tom012345；2. 密码输入"123456"；3. 点击"登录"按钮</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> username = "Tom012345"，password = "123456"</t>
+    <r>
+      <t xml:space="preserve"> 1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="1"/>
+      </rPr>
+      <t>用户名输入框输入</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="1"/>
+      </rPr>
+      <t>Tom012345</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="1"/>
+      </rPr>
+      <t>；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="1"/>
+      </rPr>
+      <t>密码输入</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="1"/>
+      </rPr>
+      <t>"123456"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="1"/>
+      </rPr>
+      <t>；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="1"/>
+      </rPr>
+      <t>点击</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="1"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="1"/>
+      </rPr>
+      <t>登录</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="1"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="1"/>
+      </rPr>
+      <t>按钮</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> username = "Tom012345"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="1"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="1"/>
+      </rPr>
+      <t>password = "123456"</t>
+    </r>
   </si>
   <si>
     <t>登录成功，进入首页</t>
@@ -247,7 +371,113 @@
     <t>系统已启动，测试账号已注册在数据库中，处于登录页</t>
   </si>
   <si>
-    <t xml:space="preserve"> 1. 用户名输入框输入Tom012345；2. 密码输入"123456"；3.点击"登录"按钮</t>
+    <r>
+      <t xml:space="preserve"> 1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="1"/>
+      </rPr>
+      <t>用户名输入框输入</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="1"/>
+      </rPr>
+      <t>Tom012345</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="1"/>
+      </rPr>
+      <t>；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="1"/>
+      </rPr>
+      <t>密码输入</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="1"/>
+      </rPr>
+      <t>"123456"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="1"/>
+      </rPr>
+      <t>；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="1"/>
+      </rPr>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="1"/>
+      </rPr>
+      <t>点击</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="1"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="1"/>
+      </rPr>
+      <t>登录</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="1"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="1"/>
+      </rPr>
+      <t>按钮</t>
+    </r>
   </si>
   <si>
     <t>主页面显示欢迎信息</t>
@@ -989,6 +1219,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve"> username = "Tom1"</t>
     </r>
     <r>
@@ -2642,7 +2877,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2680,6 +2915,12 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2688,9 +2929,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3374,7 +3612,7 @@
       <c r="E7" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="14" t="s">
         <v>34</v>
       </c>
       <c r="G7" s="11" t="s">
@@ -3383,7 +3621,7 @@
       <c r="H7" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="I7" s="14" t="s">
         <v>37</v>
       </c>
       <c r="J7" s="10" t="s">
@@ -3409,7 +3647,7 @@
       <c r="E8" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="14" t="s">
         <v>41</v>
       </c>
       <c r="G8" s="11" t="s">
@@ -3418,10 +3656,10 @@
       <c r="H8" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="J8" s="10" t="s">
+      <c r="J8" s="14" t="s">
         <v>43</v>
       </c>
       <c r="K8" s="12" t="s">
@@ -3443,7 +3681,7 @@
       <c r="C10" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="15" t="s">
         <v>48</v>
       </c>
       <c r="E10" s="9" t="s">
@@ -3478,25 +3716,25 @@
       <c r="C11" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G11" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="H11" s="14" t="s">
+      <c r="H11" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="I11" s="15" t="s">
+      <c r="I11" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="J11" s="15" t="s">
+      <c r="J11" s="17" t="s">
         <v>58</v>
       </c>
       <c r="K11" s="12" t="s">
@@ -3513,25 +3751,25 @@
       <c r="C12" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="G12" s="14" t="s">
+      <c r="G12" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="H12" s="14" t="s">
+      <c r="H12" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="I12" s="14" t="s">
+      <c r="I12" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="J12" s="14" t="s">
+      <c r="J12" s="16" t="s">
         <v>64</v>
       </c>
       <c r="K12" s="12" t="s">
@@ -3588,7 +3826,7 @@
       <c r="C15" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="14" t="s">
         <v>76</v>
       </c>
       <c r="E15" s="9" t="s">
@@ -3606,7 +3844,7 @@
       <c r="I15" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="J15" s="16" t="s">
+      <c r="J15" s="14" t="s">
         <v>80</v>
       </c>
       <c r="K15" s="12" t="s">
@@ -3768,25 +4006,25 @@
       <c r="C21" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="D21" s="15" t="s">
+      <c r="D21" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="E21" s="15" t="s">
+      <c r="E21" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="F21" s="17" t="s">
+      <c r="F21" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="G21" s="14" t="s">
+      <c r="G21" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="H21" s="14" t="s">
+      <c r="H21" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="I21" s="15" t="s">
+      <c r="I21" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="J21" s="15" t="s">
+      <c r="J21" s="17" t="s">
         <v>110</v>
       </c>
       <c r="K21" s="12" t="s">
@@ -3878,25 +4116,25 @@
       <c r="C25" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="D25" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="E25" s="18" t="s">
+      <c r="E25" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="F25" s="14" t="s">
+      <c r="F25" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="G25" s="14" t="s">
+      <c r="G25" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="H25" s="14" t="s">
+      <c r="H25" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="I25" s="14" t="s">
+      <c r="I25" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="J25" s="14" t="s">
+      <c r="J25" s="16" t="s">
         <v>128</v>
       </c>
       <c r="K25" s="12" t="s">
@@ -3918,7 +4156,7 @@
       <c r="C27" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="D27" s="19" t="s">
+      <c r="D27" s="20" t="s">
         <v>133</v>
       </c>
       <c r="E27" s="9" t="s">
